--- a/Test_Cases/05_Player/PDF_Worksheet_Player_Test_Cases.xlsx
+++ b/Test_Cases/05_Player/PDF_Worksheet_Player_Test_Cases.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
-    <col width="78" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="84" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1098,8 +1098,669 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Verify all pages of a multi-page worksheet render</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page rendering</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page worksheet available.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page worksheet</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open worksheet.
+2. Wait for render.
+3. Inspect each page.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>All pages are present and render correctly.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet remains open.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Verify single-page worksheet renders without navigation issue</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Single page</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Single-page worksheet available.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Single-page worksheet</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1. Open worksheet.
+2. Observe page/navigation.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Single page renders correctly without broken navigation.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet remains usable.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Verify worksheet document is sharp at default zoom</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Rendering quality</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>UI / Functional</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet open.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Text-heavy worksheet</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open worksheet.
+2. Observe text at default zoom.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Document text is sharp and readable at default zoom.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet remains open.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Verify continuous scrolling works with page controls</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Scrolling</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page worksheet open.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page worksheet</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1. Scroll continuously through document.
+2. Use page controls.
+3. Observe page position.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Continuous scrolling and page controls work together.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Correct page/content remains visible.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Verify next/previous controls stop at document boundaries</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Boundary navigation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page worksheet open.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page worksheet</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to first page.
+2. Attempt previous.
+3. Navigate to last page.
+4. Attempt next.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Navigation does not move beyond first or last page.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Boundary page remains selected.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Verify worksheet without answer version hides answer-key toggle</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>No answer key</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet has no answer version.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet without answer key</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1. Open worksheet.
+2. Observe controls.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Answer-key toggle is not offered.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet remains usable.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Verify first answer-key request performs lazy load</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Answer key lazy loading</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet has answer version.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet with answer key</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1. Open worksheet.
+2. Do not open answer key initially.
+3. Observe network/load behavior.
+4. Select answer key for the first time.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Answer document is fetched only when first requested and loads successfully.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Answer version is displayed.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Verify switching between answers and questions preserves correct worksheet</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Answer switching</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Answer version is loaded.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet with answer key</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1. Open answer key.
+2. Switch back to questions.
+3. Switch to answers again.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Correct question/answer documents are shown; later switches do not reload unnecessarily.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Selected document remains visible.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Verify question annotations remain predictable when switching answer key</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Answer annotations</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet with answer key; annotation tools available.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Annotated worksheet</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1. Draw annotation on question page.
+2. Switch to answers.
+3. Switch back to questions.
+4. Observe annotation.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Annotations behave consistently with the worksheet page and do not become incorrectly positioned.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Question view remains usable.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Verify orientation change keeps existing annotations aligned</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Orientation annotation</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet has existing annotation.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Annotated worksheet</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1. Draw on page.
+2. Change to landscape.
+3. Change back to portrait.
+4. Observe annotation.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Document is re-fitted and annotations remain aligned with the correct page.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Annotations remain usable.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Verify annotations remain attached to correct page after navigation</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Page annotation</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Multi-page worksheet open with annotation tools.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Annotated multi-page worksheet</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1. Draw on page 1.
+2. Navigate to page 2.
+3. Return to page 1.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Annotation remains attached to page 1 and does not appear on the wrong page.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Page annotation state is correct.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TC-PDF-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Verify worksheet download failure does not leave permanent spinner</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>A worksheet download can be failed.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Unavailable worksheet</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1. Open failing worksheet.
+2. Observe loading state.
+3. Wait for failure.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Player reports/handles failure rather than showing an indefinite spinner.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Failure is visible and recoverable.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1110,17 +1771,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1385,8 +2046,272 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-PDF-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verify all pages of a multi-page worksheet render</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-PDF-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Verify single-page worksheet renders without navigation issue</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-PDF-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Verify worksheet document is sharp at default zoom</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-PDF-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verify continuous scrolling works with page controls</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-PDF-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Verify next/previous controls stop at document boundaries</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-PDF-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Verify worksheet without answer version hides answer-key toggle</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-PDF-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Verify first answer-key request performs lazy load</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-PDF-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Verify switching between answers and questions preserves correct worksheet</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-PDF-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Verify question annotations remain predictable when switching answer key</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-PDF-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Verify orientation change keeps existing annotations aligned</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-PDF-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Verify annotations remain attached to correct page after navigation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-PDF-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Verify worksheet download failure does not leave permanent spinner</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>